--- a/module 3 functions.xlsx
+++ b/module 3 functions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7ef6ed7c7ee25d2f/Desktop/Advance_excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E21508BA-1DB6-4A19-B73A-38CBC1DC11EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="30" documentId="8_{E21508BA-1DB6-4A19-B73A-38CBC1DC11EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5A0535E0-8003-4D60-A237-2E32E7716CD1}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{A4AA22DB-7CEE-4FCB-AF78-608A8516593D}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="9" xr2:uid="{A4AA22DB-7CEE-4FCB-AF78-608A8516593D}"/>
   </bookViews>
   <sheets>
     <sheet name="If" sheetId="1" r:id="rId1"/>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="46">
   <si>
     <t>Name</t>
   </si>
@@ -197,13 +197,19 @@
   </si>
   <si>
     <t>Accounts &amp; Billing</t>
+  </si>
+  <si>
+    <t>index</t>
+  </si>
+  <si>
+    <t>match</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -260,6 +266,14 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="7">
@@ -356,7 +370,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -399,6 +413,8 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1705,10 +1721,10 @@
     <col min="6" max="6" width="6.88671875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="5.33203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.33203125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="30.33203125" style="1" customWidth="1"/>
     <col min="11" max="11" width="5.77734375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="27.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="4" spans="2:12" x14ac:dyDescent="0.3">
@@ -1766,13 +1782,22 @@
         <v>60</v>
       </c>
       <c r="H5" s="1">
-        <v>1.2</v>
+        <v>57</v>
       </c>
       <c r="I5" s="1">
-        <v>3</v>
+        <f>SUM(D5:H5)</f>
+        <v>257</v>
+      </c>
+      <c r="J5" s="1" t="str" cm="1">
+        <f t="array" ref="J5">IF(OR(AND(D5:H5&gt;33),(I5&gt;260)),"pass","fail")</f>
+        <v>fail</v>
       </c>
       <c r="K5" s="1">
         <v>10</v>
+      </c>
+      <c r="L5" s="1" t="str" cm="1">
+        <f t="array" ref="L5">IF(OR(AND(F5:J5&gt;33),(I5+K$5&gt;260)),"pass","fail")</f>
+        <v>pass</v>
       </c>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.3">
@@ -1797,7 +1822,19 @@
       <c r="H6" s="1">
         <v>99</v>
       </c>
+      <c r="I6" s="1">
+        <f>SUM(D6:H6)</f>
+        <v>399</v>
+      </c>
+      <c r="J6" s="1" t="str" cm="1">
+        <f t="array" ref="J6">IF(OR(AND(D6:H6&gt;33),(I6&gt;260)),"pass","fail")</f>
+        <v>pass</v>
+      </c>
       <c r="K6" s="1"/>
+      <c r="L6" s="1" t="str" cm="1">
+        <f t="array" ref="L6">IF(OR(AND(F6:J6&gt;33),(I6+K$5&gt;260)),"pass","fail")</f>
+        <v>pass</v>
+      </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B7" s="1">
@@ -1821,6 +1858,18 @@
       <c r="H7" s="1">
         <v>77</v>
       </c>
+      <c r="I7" s="1">
+        <f t="shared" ref="I7:I9" si="0">SUM(D7:H7)</f>
+        <v>254</v>
+      </c>
+      <c r="J7" s="1" t="str" cm="1">
+        <f t="array" ref="J7">IF(OR(AND(D7:H7&gt;33),(I7&gt;260)),"pass","fail")</f>
+        <v>fail</v>
+      </c>
+      <c r="L7" s="1" t="str" cm="1">
+        <f t="array" ref="L7">IF(OR(AND(F7:J7&gt;33),(I7+K$5&gt;260)),"pass","fail")</f>
+        <v>pass</v>
+      </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B8" s="1">
@@ -1844,6 +1893,18 @@
       <c r="H8" s="1">
         <v>88</v>
       </c>
+      <c r="I8" s="1">
+        <f t="shared" si="0"/>
+        <v>374</v>
+      </c>
+      <c r="J8" s="1" t="str" cm="1">
+        <f t="array" ref="J8">IF(OR(AND(D8:H8&gt;33),(I8&gt;260)),"pass","fail")</f>
+        <v>pass</v>
+      </c>
+      <c r="L8" s="1" t="str" cm="1">
+        <f t="array" ref="L8">IF(OR(AND(F8:J8&gt;33),(I8+K$5&gt;260)),"pass","fail")</f>
+        <v>pass</v>
+      </c>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B9" s="1">
@@ -1866,6 +1927,18 @@
       </c>
       <c r="H9" s="1">
         <v>67</v>
+      </c>
+      <c r="I9" s="1">
+        <f t="shared" si="0"/>
+        <v>255</v>
+      </c>
+      <c r="J9" s="1" t="str" cm="1">
+        <f t="array" ref="J9">IF(OR(AND(D9:H9&gt;33),(I9&gt;260)),"pass","fail")</f>
+        <v>pass</v>
+      </c>
+      <c r="L9" s="1" t="str" cm="1">
+        <f t="array" ref="L9">IF(OR(AND(F9:J9&gt;33),(I9+K$5&gt;260)),"pass","fail")</f>
+        <v>pass</v>
       </c>
     </row>
   </sheetData>
@@ -1875,10 +1948,10 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B150BCA-D215-48AB-AF5D-5A13DF4E892A}">
-  <dimension ref="C7:I12"/>
+  <dimension ref="C7:M13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="7" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C7" s="3" t="s">
         <v>7</v>
       </c>
@@ -1901,7 +1974,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="3:13" ht="23.4" x14ac:dyDescent="0.45">
       <c r="C8" s="1">
         <v>1</v>
       </c>
@@ -1923,8 +1996,11 @@
       <c r="I8" s="1">
         <v>90</v>
       </c>
-    </row>
-    <row r="9" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="K8" s="21" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C9" s="1">
         <v>2</v>
       </c>
@@ -1947,7 +2023,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="10" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C10" s="1">
         <v>3</v>
       </c>
@@ -1969,8 +2045,16 @@
       <c r="I10" s="1">
         <v>77</v>
       </c>
-    </row>
-    <row r="11" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="K10">
+        <f>INDEX(C7:I12,2,6)</f>
+        <v>60</v>
+      </c>
+      <c r="M10">
+        <f>INDEX(C7:I12,6,5)</f>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="11" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C11" s="1">
         <v>4</v>
       </c>
@@ -1993,7 +2077,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="12" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C12" s="1">
         <v>5</v>
       </c>
@@ -2014,6 +2098,16 @@
       </c>
       <c r="I12" s="1">
         <v>67</v>
+      </c>
+      <c r="K12" t="str">
+        <f>INDEX(C7:I12,1,1)</f>
+        <v>S.NO.</v>
+      </c>
+    </row>
+    <row r="13" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="M13" t="str">
+        <f>INDEX(C7:I12,1,2)</f>
+        <v>Name</v>
       </c>
     </row>
   </sheetData>
@@ -2023,10 +2117,10 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6E68639-EE2C-4779-ACA7-C8E565E048B5}">
-  <dimension ref="C6:I11"/>
+  <dimension ref="C6:M12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="6" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C6" s="3" t="s">
         <v>7</v>
       </c>
@@ -2049,7 +2143,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C7" s="1">
         <v>1</v>
       </c>
@@ -2071,8 +2165,11 @@
       <c r="I7" s="1">
         <v>90</v>
       </c>
-    </row>
-    <row r="8" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="K7" s="20" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C8" s="1">
         <v>2</v>
       </c>
@@ -2095,7 +2192,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="9" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C9" s="1">
         <v>3</v>
       </c>
@@ -2117,8 +2214,16 @@
       <c r="I9" s="1">
         <v>77</v>
       </c>
-    </row>
-    <row r="10" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="K9">
+        <f>MATCH(E8,C8:I8)</f>
+        <v>3</v>
+      </c>
+      <c r="M9">
+        <f>MATCH(C7,C6:C11,0)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C10" s="1">
         <v>4</v>
       </c>
@@ -2141,7 +2246,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="11" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C11" s="1">
         <v>5</v>
       </c>
@@ -2162,6 +2267,16 @@
       </c>
       <c r="I11" s="1">
         <v>67</v>
+      </c>
+      <c r="M11">
+        <f>MATCH(F10,F6:F11,0)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="K12">
+        <f>MATCH(C6,C6:I6,0)</f>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
